--- a/Assets/Data/Excel/WaveShopConfig.xlsx
+++ b/Assets/Data/Excel/WaveShopConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D663F32C-C6C5-4AB6-981B-26BA2BDB5B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208C758E-B35B-4D19-A6FE-4912C96B38F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4185" yWindow="3675" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>wave</t>
   </si>
@@ -102,6 +102,18 @@
   </si>
   <si>
     <t>20, 50, 30</t>
+  </si>
+  <si>
+    <t>50, 50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tier_1, Tier_2, Tier_3, Tier_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20, 20, 30, 30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -426,10 +438,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="12.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14.375" customWidth="1"/>
+    <col min="5" max="5" width="23.875" customWidth="1"/>
+    <col min="6" max="6" width="25.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -523,7 +537,7 @@
         <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
         <v>18</v>
@@ -550,6 +564,26 @@
       </c>
       <c r="F6" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
